--- a/outputs/monitor_xlsx/20260122.xlsx
+++ b/outputs/monitor_xlsx/20260122.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1113,40 +1116,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1204,12 +1202,7 @@
       <c r="O4" t="n">
         <v>-0.19</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1247,12 +1240,7 @@
       <c r="N5" t="n">
         <v>-20701</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1310,12 +1298,7 @@
       <c r="O6" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1373,12 +1356,7 @@
       <c r="O7" t="n">
         <v>12.06</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1436,12 +1414,7 @@
       <c r="O8" t="n">
         <v>1.09</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1499,12 +1472,7 @@
       <c r="O9" t="n">
         <v>-3.37</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1562,12 +1530,7 @@
       <c r="O10" t="n">
         <v>4.4</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1625,12 +1588,7 @@
       <c r="O11" t="n">
         <v>-2.12</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1688,12 +1646,7 @@
       <c r="O12" t="n">
         <v>2.29</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1751,12 +1704,7 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1814,12 +1762,7 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1877,12 +1820,7 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1940,12 +1878,7 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2003,12 +1936,7 @@
       <c r="O17" t="n">
         <v>4.26</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2063,12 +1991,7 @@
       <c r="O18" t="n">
         <v>7.36</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2126,12 +2049,7 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2186,12 +2104,7 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/outputs/monitor_xlsx/20260122.xlsx
+++ b/outputs/monitor_xlsx/20260122.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1158,7 +1155,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1172,20 +1169,20 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>101703</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-5904</v>
       </c>
       <c r="H4" t="n">
-        <v>-152462</v>
+        <v>-143552</v>
       </c>
       <c r="I4" t="n">
         <v>300</v>
       </c>
       <c r="J4" t="n">
-        <v>-5307</v>
+        <v>-5007</v>
       </c>
       <c r="K4" t="n">
         <v>55052</v>
@@ -1194,13 +1191,13 @@
         <v>7709</v>
       </c>
       <c r="M4" t="n">
-        <v>38917</v>
+        <v>38831</v>
       </c>
       <c r="N4" t="n">
         <v>-3935423</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.19</v>
+        <v>0.84</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1262,26 +1259,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1080</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>5.37</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>8441</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>-284</v>
       </c>
       <c r="H6" t="n">
-        <v>2410</v>
+        <v>798</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>1131</v>
+        <v>818</v>
       </c>
       <c r="K6" t="n">
         <v>175</v>
@@ -1290,13 +1287,13 @@
         <v>2939</v>
       </c>
       <c r="M6" t="n">
-        <v>15793</v>
+        <v>15451</v>
       </c>
       <c r="N6" t="n">
         <v>-78564</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>18.94</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1320,26 +1317,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1245</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>9.69</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>20586</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>3200</v>
       </c>
       <c r="H7" t="n">
-        <v>6572</v>
+        <v>10795</v>
       </c>
       <c r="I7" t="n">
         <v>779</v>
       </c>
       <c r="J7" t="n">
-        <v>-90</v>
+        <v>776</v>
       </c>
       <c r="K7" t="n">
         <v>581</v>
@@ -1348,13 +1345,13 @@
         <v>8789</v>
       </c>
       <c r="M7" t="n">
-        <v>41975</v>
+        <v>43137</v>
       </c>
       <c r="N7" t="n">
         <v>-648396</v>
       </c>
       <c r="O7" t="n">
-        <v>12.06</v>
+        <v>14.41</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1378,26 +1375,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1760</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1.15</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>34437</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-5350</v>
       </c>
       <c r="H8" t="n">
-        <v>-31688</v>
+        <v>-26688</v>
       </c>
       <c r="I8" t="n">
         <v>421</v>
       </c>
       <c r="J8" t="n">
-        <v>-3229</v>
+        <v>-4090</v>
       </c>
       <c r="K8" t="n">
         <v>396</v>
@@ -1406,13 +1403,13 @@
         <v>21119</v>
       </c>
       <c r="M8" t="n">
-        <v>106764</v>
+        <v>104831</v>
       </c>
       <c r="N8" t="n">
         <v>-6482795</v>
       </c>
       <c r="O8" t="n">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1494,26 +1491,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>1660</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>6.41</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3886</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1573</v>
       </c>
       <c r="H10" t="n">
-        <v>871</v>
+        <v>3900</v>
       </c>
       <c r="I10" t="n">
         <v>-78</v>
       </c>
       <c r="J10" t="n">
-        <v>-1518</v>
+        <v>-1255</v>
       </c>
       <c r="K10" t="n">
         <v>174</v>
@@ -1522,13 +1519,13 @@
         <v>2172</v>
       </c>
       <c r="M10" t="n">
-        <v>12625</v>
+        <v>12082</v>
       </c>
       <c r="N10" t="n">
         <v>-89482</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1610,26 +1607,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>1295</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>2466</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>136</v>
       </c>
       <c r="H12" t="n">
-        <v>-587</v>
+        <v>-230</v>
       </c>
       <c r="I12" t="n">
         <v>52</v>
       </c>
       <c r="J12" t="n">
-        <v>-131</v>
+        <v>-70</v>
       </c>
       <c r="K12" t="n">
         <v>52</v>
@@ -1638,13 +1635,13 @@
         <v>5038</v>
       </c>
       <c r="M12" t="n">
-        <v>26705</v>
+        <v>26165</v>
       </c>
       <c r="N12" t="n">
         <v>-19177</v>
       </c>
       <c r="O12" t="n">
-        <v>2.29</v>
+        <v>-1.55</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1668,26 +1665,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1390</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>-5.76</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6399</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-367</v>
       </c>
       <c r="H13" t="n">
-        <v>1362</v>
+        <v>970</v>
       </c>
       <c r="I13" t="n">
         <v>281</v>
       </c>
       <c r="J13" t="n">
-        <v>668</v>
+        <v>953</v>
       </c>
       <c r="K13" t="n">
         <v>-104</v>
@@ -1696,7 +1693,7 @@
         <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>-493</v>
+        <v>-424</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1842,26 +1839,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4583</v>
+      <c r="D16" s="6" t="n">
+        <v>586</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-3570</v>
       </c>
       <c r="H16" t="n">
-        <v>-2594</v>
+        <v>-5847</v>
       </c>
       <c r="I16" t="n">
         <v>165</v>
       </c>
       <c r="J16" t="n">
-        <v>2480</v>
+        <v>2780</v>
       </c>
       <c r="K16" t="n">
         <v>-118</v>
@@ -1870,7 +1867,7 @@
         <v>-652</v>
       </c>
       <c r="M16" t="n">
-        <v>-297</v>
+        <v>-636</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2008,46 +2005,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>1150</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" s="6" t="n">
         <v>7228</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>-590</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" t="n">
         <v>544</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>-451</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>-1597</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>156</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>2614</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>12769</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-140155</v>
       </c>
-      <c r="N19" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
+      <c r="O19" t="n">
+        <v>-4.17</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2174,46 +2171,46 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>962</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F22" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G22" s="6" t="n">
         <v>-80</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-218</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>3</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-2</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-37</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>31</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-143</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+      <c r="O22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2267,6 +2264,218 @@
         <is>
           <t>偏空</t>
         </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>2785</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2596</v>
+      </c>
+      <c r="I24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1258</v>
+      </c>
+      <c r="K24" t="n">
+        <v>55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>918</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4483</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-106257</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>709</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-164</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J25" t="n">
+        <v>294</v>
+      </c>
+      <c r="K25" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" t="n">
+        <v>406</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2103</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-8861</v>
+      </c>
+      <c r="O25" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>384</v>
+      </c>
+      <c r="H26" t="n">
+        <v>913</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3984</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>348</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1107</v>
+      </c>
+      <c r="I27" t="n">
+        <v>53</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-527</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6515</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33408</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-21413</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.01</v>
       </c>
     </row>
   </sheetData>
